--- a/clusters_para_interpretar.xlsx
+++ b/clusters_para_interpretar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/summa/Documents/GitHub/ci0103/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AACF457-DF8E-6B41-8476-3506843F23D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6278CA-9125-5E45-A565-5A9C2105DF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -192,7 +192,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9995C888-5CE4-F54B-96B5-72C1F83B5097}" name="Table1" displayName="Table1" ref="A1:F75" totalsRowShown="0">
-  <autoFilter ref="A1:F75" xr:uid="{9995C888-5CE4-F54B-96B5-72C1F83B5097}"/>
+  <autoFilter ref="A1:F75" xr:uid="{9995C888-5CE4-F54B-96B5-72C1F83B5097}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{1CE50FC6-020A-C148-B353-554C2A2642DA}" name="union_clusters"/>
     <tableColumn id="2" xr3:uid="{4C405EFF-E85A-E547-8ADF-AAD534368E7D}" name="cluster"/>
@@ -495,7 +501,7 @@
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
     <col min="3" max="3" width="9.83203125" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="4" max="4" width="39.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" customWidth="1"/>
     <col min="6" max="6" width="24.33203125" style="1" customWidth="1"/>
   </cols>
@@ -520,7 +526,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -540,7 +546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -560,7 +566,7 @@
         <v>0.62886161658908168</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -780,7 +786,7 @@
         <v>0.53189726594863296</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>3</v>
       </c>
@@ -800,7 +806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>3</v>
       </c>
@@ -820,7 +826,7 @@
         <v>0.66496424923391217</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>3</v>
       </c>
@@ -840,7 +846,7 @@
         <v>0.61746680286006128</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>3</v>
       </c>
@@ -860,7 +866,7 @@
         <v>0.57660878447395303</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
@@ -880,7 +886,7 @@
         <v>0.51634320735444328</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
@@ -900,7 +906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
@@ -920,7 +926,7 @@
         <v>0.69764751253374468</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
@@ -940,7 +946,7 @@
         <v>0.57038179714616277</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
@@ -960,7 +966,7 @@
         <v>0.54685692248360973</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>5</v>
       </c>
@@ -980,7 +986,7 @@
         <v>0.91806836679327186</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>5</v>
       </c>
@@ -1000,7 +1006,7 @@
         <v>0.75094953879544224</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>5</v>
       </c>
@@ -1020,7 +1026,7 @@
         <v>0.74823657080846451</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>5</v>
       </c>
@@ -1040,7 +1046,7 @@
         <v>0.65056972327726537</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>5</v>
       </c>
@@ -1060,7 +1066,7 @@
         <v>0.64677156809549652</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>5</v>
       </c>
@@ -1080,7 +1086,7 @@
         <v>0.6066196418882257</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>5</v>
       </c>
@@ -1100,7 +1106,7 @@
         <v>0.58817145957677697</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>5</v>
       </c>
@@ -1120,7 +1126,7 @@
         <v>0.57080846446011935</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
@@ -1140,7 +1146,7 @@
         <v>0.54422137818773741</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>6</v>
       </c>
@@ -1160,7 +1166,7 @@
         <v>0.97319148936170208</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>6</v>
       </c>
@@ -1180,7 +1186,7 @@
         <v>0.81574468085106377</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>6</v>
       </c>
@@ -1200,7 +1206,7 @@
         <v>0.80553191489361697</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>6</v>
       </c>
@@ -1220,7 +1226,7 @@
         <v>0.75914893617021273</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
@@ -1240,7 +1246,7 @@
         <v>0.6985106382978723</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
@@ -1260,7 +1266,7 @@
         <v>0.66340425531914893</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -1280,7 +1286,7 @@
         <v>0.52872340425531916</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
@@ -1300,7 +1306,7 @@
         <v>0.51659574468085101</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>6</v>
       </c>
@@ -1320,7 +1326,7 @@
         <v>0.50765957446808507</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
@@ -1340,7 +1346,7 @@
         <v>0.92738095238095242</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
@@ -1360,7 +1366,7 @@
         <v>0.86904761904761907</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>7</v>
       </c>
@@ -1380,7 +1386,7 @@
         <v>0.8484126984126984</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>7</v>
       </c>
@@ -1400,7 +1406,7 @@
         <v>0.75515873015873014</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>7</v>
       </c>
@@ -1420,7 +1426,7 @@
         <v>0.75277777777777777</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>7</v>
       </c>
@@ -1440,7 +1446,7 @@
         <v>0.71031746031746035</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>7</v>
       </c>
@@ -1460,7 +1466,7 @@
         <v>0.66825396825396821</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>7</v>
       </c>
@@ -1480,7 +1486,7 @@
         <v>0.65793650793650793</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>7</v>
       </c>
@@ -1500,7 +1506,7 @@
         <v>0.6432539682539683</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>7</v>
       </c>
@@ -1520,7 +1526,7 @@
         <v>0.52261904761904765</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>7</v>
       </c>
@@ -1540,7 +1546,7 @@
         <v>0.51706349206349211</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
@@ -1560,7 +1566,7 @@
         <v>0.51547619047619042</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>7</v>
       </c>
@@ -1580,7 +1586,7 @@
         <v>0.50436507936507935</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>6</v>
       </c>
@@ -1600,7 +1606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>6</v>
       </c>
@@ -1620,7 +1626,7 @@
         <v>0.6380527684875511</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>6</v>
       </c>
@@ -1640,7 +1646,7 @@
         <v>0.63507989594946113</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>6</v>
       </c>
@@ -1660,7 +1666,7 @@
         <v>0.63433667781493863</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>6</v>
       </c>
@@ -1680,7 +1686,7 @@
         <v>0.63136380527684877</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>6</v>
       </c>
@@ -1700,7 +1706,7 @@
         <v>0.63024897807506508</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>6</v>
       </c>
@@ -1800,7 +1806,7 @@
         <v>0.50701334245638041</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>11</v>
       </c>
@@ -1820,7 +1826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>11</v>
       </c>
@@ -1840,7 +1846,7 @@
         <v>0.74399164054336464</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>11</v>
       </c>
@@ -1860,7 +1866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>11</v>
       </c>
@@ -1880,7 +1886,7 @@
         <v>0.68047808764940243</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>13</v>
       </c>
@@ -1900,7 +1906,7 @@
         <v>0.83597883597883593</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>13</v>
       </c>
@@ -1920,7 +1926,7 @@
         <v>0.81422692533803642</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>13</v>
       </c>
@@ -1940,7 +1946,7 @@
         <v>0.58318636096413878</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>13</v>
       </c>
@@ -1960,7 +1966,7 @@
         <v>0.54379776601998819</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>13</v>
       </c>
@@ -1980,7 +1986,7 @@
         <v>0.53850676072898296</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>13</v>
       </c>
